--- a/results-summarized/summary-Irish-morf-xsk.xlsx
+++ b/results-summarized/summary-Irish-morf-xsk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kowk/Dropbox/GitHub/ngram-based-noun-classification/results-summarized/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F6BD12-CF00-3540-8CA8-572BDF606250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FB0FCF-A3D2-A74A-B996-220A74D8A6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1400" yWindow="500" windowWidth="35340" windowHeight="19800" xr2:uid="{152E20C4-60D5-8A45-BC95-4D78F2239C2D}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -220,223 +220,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="132">
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <fill>
@@ -708,12 +498,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -727,12 +511,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -746,12 +524,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -765,12 +537,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -784,12 +550,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -803,12 +563,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -822,12 +576,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -841,12 +589,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -860,12 +602,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -879,12 +615,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -898,12 +628,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -917,12 +641,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -936,12 +654,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -955,294 +667,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -1683,7 +1107,892 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -1878,316 +2187,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2473,6 +2473,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$3:$V$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.68</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -2555,6 +2595,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$4:$V$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.68</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -2637,6 +2717,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$5:$V$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.66</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -2801,6 +2921,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$7:$V$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.71</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -2885,6 +3045,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$8:$V$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.66</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -2969,6 +3169,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$9:$V$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.71</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -3137,6 +3377,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$11:$V$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.72</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -3305,6 +3585,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$13:$V$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -3560,6 +3880,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$16:$V$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.67</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -3730,6 +4090,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$18:$V$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.67</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -3815,6 +4215,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$19:$V$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -3899,6 +4339,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$20:$V$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.71</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -3983,6 +4463,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$21:$V$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.66</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -4067,6 +4587,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$22:$V$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.68</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -5321,6 +5881,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$34:$V$34</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.79</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -5405,6 +6005,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$35:$V$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.75</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -5489,6 +6129,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$36:$V$36</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.73</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -5783,6 +6463,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$39:$V$39</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.76</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -6038,6 +6758,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$42:$V$42</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -6207,6 +6967,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$44:$V$44</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.77</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -6291,6 +7091,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$45:$V$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.71</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -6543,6 +7383,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$48:$V$48</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.97</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -6627,6 +7507,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$49:$V$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.98</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -6712,6 +7632,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$50:$V$50</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.96</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -6797,6 +7757,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$51:$V$51</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.97</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -6882,6 +7882,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$52:$V$52</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.96</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -6967,6 +8007,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$53:$V$53</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.98</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -7052,6 +8132,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$54:$V$54</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.96</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -7137,6 +8257,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$55:$V$55</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.96</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -7383,6 +8543,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$58:$V$58</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.94</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -7465,6 +8665,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$59:$V$59</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.94</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -7881,6 +9121,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$64:$V$64</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.97</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -7965,6 +9245,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$65:$V$65</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.97</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -8049,6 +9369,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$66:$V$66</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.95</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -8133,6 +9493,46 @@
           <c:val>
             <c:numRef>
               <c:f>summarized!$K$67:$V$67</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.95</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -8920,7 +10320,7 @@
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>535900</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>2500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -8957,16 +10357,6 @@
         <filter val="9"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="5">
-      <filters>
-        <filter val="gender"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="TRUE"/>
-      </filters>
-    </filterColumn>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:Y38">
     <sortCondition ref="A1:A67"/>
@@ -8981,26 +10371,26 @@
     <tableColumn id="7" xr3:uid="{4DF4825C-28C6-314B-8759-E970CEB4CAD4}" name="supplemented"/>
     <tableColumn id="8" xr3:uid="{33621AA7-F171-724A-A9C3-9BF051949EB2}" name="method.index"/>
     <tableColumn id="9" xr3:uid="{FA10D699-0F32-DE48-BB94-CE37B11D93FE}" name="method"/>
-    <tableColumn id="10" xr3:uid="{6AFF8DF1-CE17-4549-8240-57ED1529CE6A}" name="var" dataDxfId="1">
+    <tableColumn id="10" xr3:uid="{6AFF8DF1-CE17-4549-8240-57ED1529CE6A}" name="var" dataDxfId="131">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table10[ml]),_xlpm.sn,_xlfn.SINGLE(Table10[sample.n]),_xlpm.mgv,_xlfn.SINGLE(Table10[mgv]),_xlpm.attr,LEFT(_xlfn.SINGLE(Table10[attribute]),3),_xlpm.spl,LEFT(_xlfn.SINGLE(Table10[supplemented]),1),_xlfn.TEXTJOIN({"","-s","k-","-spl:","-mgv","x"},TRUE,"ml:",_xlpm.ml,_xlpm.sn,_xlpm.attr,_xlpm.spl,_xlpm.mgv))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2946B477-B30C-7045-AA66-E35296325F3C}" name="2g-no-hash" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{1413BA46-C7CE-5E48-A233-42F6537E9D5C}" name="3g-no-hash" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{76578E92-16DD-3341-A89C-5C6C2A738DE1}" name="4g-no-hash" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{9F7B114A-FE63-D743-8058-132F88048474}" name="xsk2g-no-hash" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{0F1E6EB1-F33F-EB43-9D77-ACA0E25FE212}" name="xsk3g-no-hash" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{41AC8B56-0D05-5C46-888E-9261FAB17C9B}" name="xsk4g-no-hash" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{EDB32EC9-624E-7944-A621-A96C1110D448}" name="2g-hash-at-both" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{86F7230F-0E33-D843-B69C-EE21854F46DC}" name="3g-hash-at-both" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{67B1E032-6102-2549-8572-690B7FC77498}" name="4g-hash-at-both" dataDxfId="7"/>
-    <tableColumn id="20" xr3:uid="{A6035794-4CB6-ED4A-9777-AD0D4308C6E1}" name="xsk2g-hash-at-both" dataDxfId="6"/>
-    <tableColumn id="21" xr3:uid="{36BB08A0-7291-F24E-8F1C-5C0D28E55B5B}" name="xsk3g-hash-at-both" dataDxfId="5"/>
-    <tableColumn id="22" xr3:uid="{28E4FC11-7348-1F49-BF86-170C8D9428EA}" name="xsk4g-hash-at-both" dataDxfId="4"/>
-    <tableColumn id="23" xr3:uid="{83613AF3-B0D1-9040-AE3C-8B84C8D42B61}" name="max" dataDxfId="3"/>
-    <tableColumn id="24" xr3:uid="{F3B525BD-C134-6942-AB85-2DB7312F6E89}" name="geomean" dataDxfId="2">
+    <tableColumn id="11" xr3:uid="{2946B477-B30C-7045-AA66-E35296325F3C}" name="2g-no-hash" dataDxfId="130"/>
+    <tableColumn id="12" xr3:uid="{1413BA46-C7CE-5E48-A233-42F6537E9D5C}" name="3g-no-hash" dataDxfId="129"/>
+    <tableColumn id="13" xr3:uid="{76578E92-16DD-3341-A89C-5C6C2A738DE1}" name="4g-no-hash" dataDxfId="128"/>
+    <tableColumn id="14" xr3:uid="{9F7B114A-FE63-D743-8058-132F88048474}" name="xsk2g-no-hash" dataDxfId="127"/>
+    <tableColumn id="15" xr3:uid="{0F1E6EB1-F33F-EB43-9D77-ACA0E25FE212}" name="xsk3g-no-hash" dataDxfId="126"/>
+    <tableColumn id="16" xr3:uid="{41AC8B56-0D05-5C46-888E-9261FAB17C9B}" name="xsk4g-no-hash" dataDxfId="125"/>
+    <tableColumn id="17" xr3:uid="{EDB32EC9-624E-7944-A621-A96C1110D448}" name="2g-hash-at-both" dataDxfId="124"/>
+    <tableColumn id="18" xr3:uid="{86F7230F-0E33-D843-B69C-EE21854F46DC}" name="3g-hash-at-both" dataDxfId="123"/>
+    <tableColumn id="19" xr3:uid="{67B1E032-6102-2549-8572-690B7FC77498}" name="4g-hash-at-both" dataDxfId="122"/>
+    <tableColumn id="20" xr3:uid="{A6035794-4CB6-ED4A-9777-AD0D4308C6E1}" name="xsk2g-hash-at-both" dataDxfId="121"/>
+    <tableColumn id="21" xr3:uid="{36BB08A0-7291-F24E-8F1C-5C0D28E55B5B}" name="xsk3g-hash-at-both" dataDxfId="120"/>
+    <tableColumn id="22" xr3:uid="{28E4FC11-7348-1F49-BF86-170C8D9428EA}" name="xsk4g-hash-at-both" dataDxfId="119"/>
+    <tableColumn id="23" xr3:uid="{83613AF3-B0D1-9040-AE3C-8B84C8D42B61}" name="max" dataDxfId="118"/>
+    <tableColumn id="24" xr3:uid="{F3B525BD-C134-6942-AB85-2DB7312F6E89}" name="geomean" dataDxfId="117">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$K2:$V2,GEOMEAN(_xlpm.d))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{E8702139-A703-FC4E-AF8D-747BDCB52DEB}" name="gm.rank" dataDxfId="0">
+    <tableColumn id="25" xr3:uid="{E8702139-A703-FC4E-AF8D-747BDCB52DEB}" name="gm.rank" dataDxfId="116">
       <calculatedColumnFormula>RANK(X2,X$2:X$67)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9018,22 +10408,22 @@
     <tableColumn id="4" xr3:uid="{2AFF2AE7-D0B4-B446-978B-4D300CB079F3}" name="supplemented"/>
     <tableColumn id="5" xr3:uid="{C30691CA-B422-5340-94E7-865A300D83FB}" name="method.index"/>
     <tableColumn id="6" xr3:uid="{07121009-9709-D548-9191-AA49D1B71CAB}" name="method"/>
-    <tableColumn id="20" xr3:uid="{EF84B8C9-B532-CD43-BD7F-FCBE9D7235A0}" name="var" dataDxfId="19">
+    <tableColumn id="20" xr3:uid="{EF84B8C9-B532-CD43-BD7F-FCBE9D7235A0}" name="var" dataDxfId="115">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.attr,Table2[[#This Row],[attribute]],_xlpm.spl,LEFT(Table2[[#This Row],[supplemented]],1),_xlfn.TEXTJOIN("-",TRUE,_xlpm.attr,_xlpm.spl,"3k-mgv3"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{630EF1DA-945D-CA4C-A355-EC3095D1BB40}" name="2g-no-hash" dataDxfId="92"/>
-    <tableColumn id="8" xr3:uid="{071DD66A-AC03-8642-A3FD-A6FD11480437}" name="3g-no-hash" dataDxfId="91"/>
-    <tableColumn id="9" xr3:uid="{7EF290FB-1EC1-0441-BC16-6703E3CB2718}" name="4g-no-hash" dataDxfId="90"/>
-    <tableColumn id="10" xr3:uid="{4C56D5EB-2B33-DE4E-826D-3946624D3028}" name="xsk2g-no-hash" dataDxfId="89"/>
-    <tableColumn id="11" xr3:uid="{006F963D-9D32-E24E-89EC-8369C3F2FAE1}" name="xsk3g-no-hash" dataDxfId="88"/>
-    <tableColumn id="12" xr3:uid="{C24F7266-C19F-BF45-B142-D5DA5D428F19}" name="xsk4g-no-hash" dataDxfId="87"/>
-    <tableColumn id="13" xr3:uid="{3608483A-C944-CA41-9312-6C8432A88C02}" name="2g-hash-at-both" dataDxfId="86"/>
-    <tableColumn id="14" xr3:uid="{7E2908DE-6597-FF4B-9345-F5BD095FD415}" name="3g-hash-at-both" dataDxfId="85"/>
-    <tableColumn id="15" xr3:uid="{006CBE99-B7A0-A546-B116-FD104BE5D6F5}" name="4g-hash-at-both" dataDxfId="84"/>
-    <tableColumn id="16" xr3:uid="{6C79B028-874A-1E42-9601-00A492DAB970}" name="xsk2g-hash-at-both" dataDxfId="83"/>
-    <tableColumn id="17" xr3:uid="{1DC0584F-705F-C04B-96D4-88A9E71D8D01}" name="xsk3g-hash-at-both" dataDxfId="82"/>
-    <tableColumn id="18" xr3:uid="{8C13FB65-9420-A640-A472-86DB34DCCD9A}" name="xsk4g-hash-at-both" dataDxfId="81"/>
-    <tableColumn id="19" xr3:uid="{BE24F56C-9016-1A40-989B-99FE6BB02E2E}" name="max" dataDxfId="80">
+    <tableColumn id="7" xr3:uid="{630EF1DA-945D-CA4C-A355-EC3095D1BB40}" name="2g-no-hash" dataDxfId="114"/>
+    <tableColumn id="8" xr3:uid="{071DD66A-AC03-8642-A3FD-A6FD11480437}" name="3g-no-hash" dataDxfId="113"/>
+    <tableColumn id="9" xr3:uid="{7EF290FB-1EC1-0441-BC16-6703E3CB2718}" name="4g-no-hash" dataDxfId="112"/>
+    <tableColumn id="10" xr3:uid="{4C56D5EB-2B33-DE4E-826D-3946624D3028}" name="xsk2g-no-hash" dataDxfId="111"/>
+    <tableColumn id="11" xr3:uid="{006F963D-9D32-E24E-89EC-8369C3F2FAE1}" name="xsk3g-no-hash" dataDxfId="110"/>
+    <tableColumn id="12" xr3:uid="{C24F7266-C19F-BF45-B142-D5DA5D428F19}" name="xsk4g-no-hash" dataDxfId="109"/>
+    <tableColumn id="13" xr3:uid="{3608483A-C944-CA41-9312-6C8432A88C02}" name="2g-hash-at-both" dataDxfId="108"/>
+    <tableColumn id="14" xr3:uid="{7E2908DE-6597-FF4B-9345-F5BD095FD415}" name="3g-hash-at-both" dataDxfId="107"/>
+    <tableColumn id="15" xr3:uid="{006CBE99-B7A0-A546-B116-FD104BE5D6F5}" name="4g-hash-at-both" dataDxfId="106"/>
+    <tableColumn id="16" xr3:uid="{6C79B028-874A-1E42-9601-00A492DAB970}" name="xsk2g-hash-at-both" dataDxfId="105"/>
+    <tableColumn id="17" xr3:uid="{1DC0584F-705F-C04B-96D4-88A9E71D8D01}" name="xsk3g-hash-at-both" dataDxfId="104"/>
+    <tableColumn id="18" xr3:uid="{8C13FB65-9420-A640-A472-86DB34DCCD9A}" name="xsk4g-hash-at-both" dataDxfId="103"/>
+    <tableColumn id="19" xr3:uid="{BE24F56C-9016-1A40-989B-99FE6BB02E2E}" name="max" dataDxfId="102">
       <calculatedColumnFormula>MAX($H2:$S2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9048,51 +10438,51 @@
     <sortCondition ref="B22:B28"/>
   </sortState>
   <tableColumns count="19">
-    <tableColumn id="18" xr3:uid="{78A7E720-84B0-B14C-AD64-981B34BA4B13}" name="attribute.index" dataDxfId="34"/>
+    <tableColumn id="18" xr3:uid="{78A7E720-84B0-B14C-AD64-981B34BA4B13}" name="attribute.index" dataDxfId="101"/>
     <tableColumn id="1" xr3:uid="{69CFB08A-B2E6-1C48-BBB7-78415099A9F3}" name="attribute"/>
     <tableColumn id="2" xr3:uid="{7772C76F-4B12-7C49-94DE-1355E72F6C6A}" name="supplemented"/>
     <tableColumn id="3" xr3:uid="{92DF0BD8-4D8F-DC45-BD7A-479F49F1F365}" name="method.index"/>
     <tableColumn id="4" xr3:uid="{6B0D794B-6BBB-644A-9C25-88BCD189248E}" name="method"/>
-    <tableColumn id="19" xr3:uid="{998CE790-803A-9D41-9B42-1310BA7D0CDA}" name="var" dataDxfId="33">
+    <tableColumn id="19" xr3:uid="{998CE790-803A-9D41-9B42-1310BA7D0CDA}" name="var" dataDxfId="100">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.attr,Table618810[[#This Row],[attribute]],_xlpm.spl,LEFT(Table618810[[#This Row],[supplemented]],1),_xlfn.TEXTJOIN("-",TRUE,_xlpm.attr,_xlpm.spl,"3k-mgv3"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CF487C83-AFDB-DA48-AFD8-4C42B90198D6}" name="2g-no-hash" dataDxfId="32">
+    <tableColumn id="5" xr3:uid="{CF487C83-AFDB-DA48-AFD8-4C42B90198D6}" name="2g-no-hash" dataDxfId="99">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{CB106F05-AFB3-5744-90DB-50DC5EFF0A9A}" name="3g-no-hash" dataDxfId="31">
+    <tableColumn id="6" xr3:uid="{CB106F05-AFB3-5744-90DB-50DC5EFF0A9A}" name="3g-no-hash" dataDxfId="98">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{580500E7-1E23-B24A-8AEC-6FB72642062C}" name="4g-no-hash" dataDxfId="30">
+    <tableColumn id="7" xr3:uid="{580500E7-1E23-B24A-8AEC-6FB72642062C}" name="4g-no-hash" dataDxfId="97">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{4C14982B-CC17-664B-9F94-87456B20E998}" name="xsk2g-no-hash" dataDxfId="29">
+    <tableColumn id="8" xr3:uid="{4C14982B-CC17-664B-9F94-87456B20E998}" name="xsk2g-no-hash" dataDxfId="96">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{86504520-266A-F74F-AAE8-489D953A4766}" name="xsk3g-no-hash" dataDxfId="28">
+    <tableColumn id="9" xr3:uid="{86504520-266A-F74F-AAE8-489D953A4766}" name="xsk3g-no-hash" dataDxfId="95">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{7F251EBE-1080-1944-A0E9-67EB4432ECF0}" name="xsk4g-no-hash" dataDxfId="27">
+    <tableColumn id="10" xr3:uid="{7F251EBE-1080-1944-A0E9-67EB4432ECF0}" name="xsk4g-no-hash" dataDxfId="94">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D9A679DB-55F4-174C-B71E-F299634E4D99}" name="2g-hash-at-both" dataDxfId="26">
+    <tableColumn id="11" xr3:uid="{D9A679DB-55F4-174C-B71E-F299634E4D99}" name="2g-hash-at-both" dataDxfId="93">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EEDBAD26-5E77-554D-9ABF-E54A370B7220}" name="3g-hash-at-both" dataDxfId="25">
+    <tableColumn id="12" xr3:uid="{EEDBAD26-5E77-554D-9ABF-E54A370B7220}" name="3g-hash-at-both" dataDxfId="92">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{1C035930-B58B-534E-B185-EA04BF103044}" name="4g-hash-at-both" dataDxfId="24">
+    <tableColumn id="13" xr3:uid="{1C035930-B58B-534E-B185-EA04BF103044}" name="4g-hash-at-both" dataDxfId="91">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{2918724C-34FE-3847-8D28-087534685EA9}" name="xsk2g-hash-at-both" dataDxfId="23">
+    <tableColumn id="14" xr3:uid="{2918724C-34FE-3847-8D28-087534685EA9}" name="xsk2g-hash-at-both" dataDxfId="90">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{0A75B223-CDE0-4F42-981D-1896157C5264}" name="xsk3g-hash-at-both" dataDxfId="22">
+    <tableColumn id="15" xr3:uid="{0A75B223-CDE0-4F42-981D-1896157C5264}" name="xsk3g-hash-at-both" dataDxfId="89">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{ED0D3A26-2816-ED43-8552-C683CD87F6AA}" name="xsk4g-hash-at-both" dataDxfId="21">
+    <tableColumn id="16" xr3:uid="{ED0D3A26-2816-ED43-8552-C683CD87F6AA}" name="xsk4g-hash-at-both" dataDxfId="88">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C997A3F3-6C7B-D94B-B772-63F20A51CB59}" name="max" dataDxfId="20">
+    <tableColumn id="17" xr3:uid="{C997A3F3-6C7B-D94B-B772-63F20A51CB59}" name="max" dataDxfId="87">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9110,22 +10500,22 @@
     <tableColumn id="4" xr3:uid="{153A37C8-64CD-904B-B6A9-F8D7037CD2EE}" name="supplemented"/>
     <tableColumn id="5" xr3:uid="{86352077-8C84-0849-A021-AD9ECDE69762}" name="method.index"/>
     <tableColumn id="6" xr3:uid="{2ECCFC5C-0CA5-6744-8855-F3529FA67B4D}" name="method"/>
-    <tableColumn id="20" xr3:uid="{698D0E1F-7D35-BC4A-A7CA-7DD9CA9B69C8}" name="var" dataDxfId="18">
+    <tableColumn id="20" xr3:uid="{698D0E1F-7D35-BC4A-A7CA-7DD9CA9B69C8}" name="var" dataDxfId="86">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.attr,Table3[[#This Row],[attribute]],_xlpm.spl,LEFT(Table3[[#This Row],[supplemented]],1),_xlfn.TEXTJOIN("-",TRUE,_xlpm.attr,_xlpm.spl,"3k-mgv3"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{542DB996-817A-AC4A-BC85-9A9DAF944E19}" name="2g-no-hash" dataDxfId="105"/>
-    <tableColumn id="8" xr3:uid="{F7CB7A67-5EF0-4C43-B849-0E75CDF7FEE9}" name="3g-no-hash" dataDxfId="104"/>
-    <tableColumn id="9" xr3:uid="{28F32EE3-B098-6A4C-ABB6-C82F988BEC90}" name="4g-no-hash" dataDxfId="103"/>
-    <tableColumn id="10" xr3:uid="{6D726EDE-3EC0-BE44-8C1E-CFF1DAC42277}" name="xsk2g-no-hash" dataDxfId="102"/>
-    <tableColumn id="11" xr3:uid="{8545F3CF-C965-854D-89EB-ECBC9F8DBF33}" name="xsk3g-no-hash" dataDxfId="101"/>
-    <tableColumn id="12" xr3:uid="{1DC0D56C-A523-674B-8270-18F78523BA64}" name="xsk4g-no-hash" dataDxfId="100"/>
-    <tableColumn id="13" xr3:uid="{73955608-1BB1-DB4E-BAE8-B32EA496725C}" name="2g-hash-at-both" dataDxfId="99"/>
-    <tableColumn id="14" xr3:uid="{A4573D50-D686-684B-A7C6-8A2C766A34E1}" name="3g-hash-at-both" dataDxfId="98"/>
-    <tableColumn id="15" xr3:uid="{E07D75A2-00D7-F74F-B3BA-0D0CF07F363F}" name="4g-hash-at-both" dataDxfId="97"/>
-    <tableColumn id="16" xr3:uid="{C7EB8FD5-5D9C-964F-B17F-E12DE4D009E7}" name="xsk2g-hash-at-both" dataDxfId="96"/>
-    <tableColumn id="17" xr3:uid="{A9CAB303-A76A-1541-9316-3DD3CE956DC9}" name="xsk3g-hash-at-both" dataDxfId="95"/>
-    <tableColumn id="18" xr3:uid="{27950F01-8F00-9B46-B10E-687292EB369A}" name="xsk4g-hash-at-both" dataDxfId="94"/>
-    <tableColumn id="19" xr3:uid="{DA1929CA-C709-0E4C-9460-8F2E773C8352}" name="max" dataDxfId="93">
+    <tableColumn id="7" xr3:uid="{542DB996-817A-AC4A-BC85-9A9DAF944E19}" name="2g-no-hash" dataDxfId="85"/>
+    <tableColumn id="8" xr3:uid="{F7CB7A67-5EF0-4C43-B849-0E75CDF7FEE9}" name="3g-no-hash" dataDxfId="84"/>
+    <tableColumn id="9" xr3:uid="{28F32EE3-B098-6A4C-ABB6-C82F988BEC90}" name="4g-no-hash" dataDxfId="83"/>
+    <tableColumn id="10" xr3:uid="{6D726EDE-3EC0-BE44-8C1E-CFF1DAC42277}" name="xsk2g-no-hash" dataDxfId="82"/>
+    <tableColumn id="11" xr3:uid="{8545F3CF-C965-854D-89EB-ECBC9F8DBF33}" name="xsk3g-no-hash" dataDxfId="81"/>
+    <tableColumn id="12" xr3:uid="{1DC0D56C-A523-674B-8270-18F78523BA64}" name="xsk4g-no-hash" dataDxfId="80"/>
+    <tableColumn id="13" xr3:uid="{73955608-1BB1-DB4E-BAE8-B32EA496725C}" name="2g-hash-at-both" dataDxfId="79"/>
+    <tableColumn id="14" xr3:uid="{A4573D50-D686-684B-A7C6-8A2C766A34E1}" name="3g-hash-at-both" dataDxfId="78"/>
+    <tableColumn id="15" xr3:uid="{E07D75A2-00D7-F74F-B3BA-0D0CF07F363F}" name="4g-hash-at-both" dataDxfId="77"/>
+    <tableColumn id="16" xr3:uid="{C7EB8FD5-5D9C-964F-B17F-E12DE4D009E7}" name="xsk2g-hash-at-both" dataDxfId="76"/>
+    <tableColumn id="17" xr3:uid="{A9CAB303-A76A-1541-9316-3DD3CE956DC9}" name="xsk3g-hash-at-both" dataDxfId="75"/>
+    <tableColumn id="18" xr3:uid="{27950F01-8F00-9B46-B10E-687292EB369A}" name="xsk4g-hash-at-both" dataDxfId="74"/>
+    <tableColumn id="19" xr3:uid="{DA1929CA-C709-0E4C-9460-8F2E773C8352}" name="max" dataDxfId="73">
       <calculatedColumnFormula>MAX($H2:$S2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9140,51 +10530,51 @@
     <sortCondition ref="B22:B28"/>
   </sortState>
   <tableColumns count="19">
-    <tableColumn id="18" xr3:uid="{241E68B1-BB1A-A648-8C2C-605FC6CB9424}" name="attribute.index" dataDxfId="49"/>
+    <tableColumn id="18" xr3:uid="{241E68B1-BB1A-A648-8C2C-605FC6CB9424}" name="attribute.index" dataDxfId="72"/>
     <tableColumn id="1" xr3:uid="{35D07776-9125-8E43-8B9E-282B7514B0BC}" name="attribute"/>
     <tableColumn id="2" xr3:uid="{BF3AE054-F405-AF4B-9034-A793D16D6645}" name="supplemented"/>
     <tableColumn id="3" xr3:uid="{7B3F3750-82A2-1946-A7CB-565A379331EE}" name="method.index"/>
     <tableColumn id="4" xr3:uid="{36221A6B-AE14-2D4C-978E-FA48CDA1B260}" name="method"/>
-    <tableColumn id="19" xr3:uid="{C8729FF7-5480-434C-B71E-7BE69260DA23}" name="var" dataDxfId="48">
+    <tableColumn id="19" xr3:uid="{C8729FF7-5480-434C-B71E-7BE69260DA23}" name="var" dataDxfId="71">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.attr,Table61889[[#This Row],[attribute]],_xlpm.spl,LEFT(Table61889[[#This Row],[supplemented]],1),_xlfn.TEXTJOIN("-",TRUE,_xlpm.attr,_xlpm.spl,"3k-mgv3"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EC6B6F11-1E6A-BD40-96B3-4C5063E7609B}" name="2g-no-hash" dataDxfId="47">
+    <tableColumn id="5" xr3:uid="{EC6B6F11-1E6A-BD40-96B3-4C5063E7609B}" name="2g-no-hash" dataDxfId="70">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{39C93787-3AC3-1740-82E2-CA39BF43591C}" name="3g-no-hash" dataDxfId="46">
+    <tableColumn id="6" xr3:uid="{39C93787-3AC3-1740-82E2-CA39BF43591C}" name="3g-no-hash" dataDxfId="69">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{DEDC621B-5D10-1848-A349-0C915D1E9C42}" name="4g-no-hash" dataDxfId="45">
+    <tableColumn id="7" xr3:uid="{DEDC621B-5D10-1848-A349-0C915D1E9C42}" name="4g-no-hash" dataDxfId="68">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{C73889FA-43F4-274D-9A9F-EBCDFE66C9A1}" name="xsk2g-no-hash" dataDxfId="44">
+    <tableColumn id="8" xr3:uid="{C73889FA-43F4-274D-9A9F-EBCDFE66C9A1}" name="xsk2g-no-hash" dataDxfId="67">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{6A0C7E39-4EE8-874C-A9BF-EBC5727E8683}" name="xsk3g-no-hash" dataDxfId="43">
+    <tableColumn id="9" xr3:uid="{6A0C7E39-4EE8-874C-A9BF-EBC5727E8683}" name="xsk3g-no-hash" dataDxfId="66">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E9332FEF-B880-DB41-9C79-0B83C6F797FF}" name="xsk4g-no-hash" dataDxfId="42">
+    <tableColumn id="10" xr3:uid="{E9332FEF-B880-DB41-9C79-0B83C6F797FF}" name="xsk4g-no-hash" dataDxfId="65">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{8E5969BC-5CDC-F94E-B1FC-0DA4EA48A25C}" name="2g-hash-at-both" dataDxfId="41">
+    <tableColumn id="11" xr3:uid="{8E5969BC-5CDC-F94E-B1FC-0DA4EA48A25C}" name="2g-hash-at-both" dataDxfId="64">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{86AF7FCC-0B41-494D-A521-28C44D70B9DA}" name="3g-hash-at-both" dataDxfId="40">
+    <tableColumn id="12" xr3:uid="{86AF7FCC-0B41-494D-A521-28C44D70B9DA}" name="3g-hash-at-both" dataDxfId="63">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{62D58BAE-378C-7647-A67A-D6DF978A1A76}" name="4g-hash-at-both" dataDxfId="39">
+    <tableColumn id="13" xr3:uid="{62D58BAE-378C-7647-A67A-D6DF978A1A76}" name="4g-hash-at-both" dataDxfId="62">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{6F0D9AAC-7D36-384D-B13D-1DA9673D42D4}" name="xsk2g-hash-at-both" dataDxfId="38">
+    <tableColumn id="14" xr3:uid="{6F0D9AAC-7D36-384D-B13D-1DA9673D42D4}" name="xsk2g-hash-at-both" dataDxfId="61">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{D97D776F-A48A-FF45-8FEB-34EC0A268E78}" name="xsk3g-hash-at-both" dataDxfId="37">
+    <tableColumn id="15" xr3:uid="{D97D776F-A48A-FF45-8FEB-34EC0A268E78}" name="xsk3g-hash-at-both" dataDxfId="60">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{61FFC45A-BBC4-0A44-A378-34063464F611}" name="xsk4g-hash-at-both" dataDxfId="36">
+    <tableColumn id="16" xr3:uid="{61FFC45A-BBC4-0A44-A378-34063464F611}" name="xsk4g-hash-at-both" dataDxfId="59">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{B807E904-FC46-9A44-B592-3E9A529884FE}" name="max" dataDxfId="35">
+    <tableColumn id="17" xr3:uid="{B807E904-FC46-9A44-B592-3E9A529884FE}" name="max" dataDxfId="58">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9202,22 +10592,22 @@
     <tableColumn id="4" xr3:uid="{9126EC1F-AFDD-784F-B150-5B23E953D469}" name="supplemented"/>
     <tableColumn id="5" xr3:uid="{AA297ADA-4C4C-CB4F-A3B9-E21DEB546B18}" name="method.index"/>
     <tableColumn id="6" xr3:uid="{213FE8E7-F556-9B45-BB8D-6980A82409D5}" name="method"/>
-    <tableColumn id="20" xr3:uid="{2946616C-8F22-EB4A-880A-3FD16DC71829}" name="var" dataDxfId="17">
+    <tableColumn id="20" xr3:uid="{2946616C-8F22-EB4A-880A-3FD16DC71829}" name="var" dataDxfId="57">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.attr,Table4[[#This Row],[attribute]],_xlpm.spl,LEFT(Table4[[#This Row],[supplemented]],1),_xlfn.TEXTJOIN("-",TRUE,_xlpm.attr,_xlpm.spl,"3k-mgv3"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{74772413-BCFE-504B-95C5-E9048143A2F4}" name="2g-no-hash" dataDxfId="118"/>
-    <tableColumn id="8" xr3:uid="{498525DE-2AAC-5247-8C64-89C2F352238A}" name="3g-no-hash" dataDxfId="117"/>
-    <tableColumn id="9" xr3:uid="{FE54B8E0-3F46-F747-A820-8634E6388EF0}" name="4g-no-hash" dataDxfId="116"/>
-    <tableColumn id="10" xr3:uid="{9DDF8A46-587F-B746-BB72-F80CFEF2A27D}" name="xsk2g-no-hash" dataDxfId="115"/>
-    <tableColumn id="11" xr3:uid="{8CD36104-D772-494A-A296-BC31574AAE78}" name="xsk3g-no-hash" dataDxfId="114"/>
-    <tableColumn id="12" xr3:uid="{7EE32F84-2FF8-EF48-9F50-EC15226B71B6}" name="xsk4g-no-hash" dataDxfId="113"/>
-    <tableColumn id="13" xr3:uid="{FC7503E0-40FA-1F43-966C-12C0158BE580}" name="2g-hash-at-both" dataDxfId="112"/>
-    <tableColumn id="14" xr3:uid="{94AD2EAC-DE28-D545-9323-0F416F4A4885}" name="3g-hash-at-both" dataDxfId="111"/>
-    <tableColumn id="15" xr3:uid="{FF6A8353-88FE-3845-B3D4-D5AFB1F26A7B}" name="4g-hash-at-both" dataDxfId="110"/>
-    <tableColumn id="16" xr3:uid="{06BAD96A-7D85-0E43-BFBC-C4C091F9C583}" name="xsk2g-hash-at-both" dataDxfId="109"/>
-    <tableColumn id="17" xr3:uid="{018F4BB2-BCDB-F246-B222-18869E547938}" name="xsk3g-hash-at-both" dataDxfId="108"/>
-    <tableColumn id="18" xr3:uid="{0A17B582-EECA-4C40-9F2A-5A570759AC6B}" name="xsk4g-hash-at-both" dataDxfId="107"/>
-    <tableColumn id="19" xr3:uid="{0A6FA590-01CE-B142-8995-01E614C22035}" name="max" dataDxfId="106">
+    <tableColumn id="7" xr3:uid="{74772413-BCFE-504B-95C5-E9048143A2F4}" name="2g-no-hash" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{498525DE-2AAC-5247-8C64-89C2F352238A}" name="3g-no-hash" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{FE54B8E0-3F46-F747-A820-8634E6388EF0}" name="4g-no-hash" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{9DDF8A46-587F-B746-BB72-F80CFEF2A27D}" name="xsk2g-no-hash" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{8CD36104-D772-494A-A296-BC31574AAE78}" name="xsk3g-no-hash" dataDxfId="52"/>
+    <tableColumn id="12" xr3:uid="{7EE32F84-2FF8-EF48-9F50-EC15226B71B6}" name="xsk4g-no-hash" dataDxfId="51"/>
+    <tableColumn id="13" xr3:uid="{FC7503E0-40FA-1F43-966C-12C0158BE580}" name="2g-hash-at-both" dataDxfId="50"/>
+    <tableColumn id="14" xr3:uid="{94AD2EAC-DE28-D545-9323-0F416F4A4885}" name="3g-hash-at-both" dataDxfId="49"/>
+    <tableColumn id="15" xr3:uid="{FF6A8353-88FE-3845-B3D4-D5AFB1F26A7B}" name="4g-hash-at-both" dataDxfId="48"/>
+    <tableColumn id="16" xr3:uid="{06BAD96A-7D85-0E43-BFBC-C4C091F9C583}" name="xsk2g-hash-at-both" dataDxfId="47"/>
+    <tableColumn id="17" xr3:uid="{018F4BB2-BCDB-F246-B222-18869E547938}" name="xsk3g-hash-at-both" dataDxfId="46"/>
+    <tableColumn id="18" xr3:uid="{0A17B582-EECA-4C40-9F2A-5A570759AC6B}" name="xsk4g-hash-at-both" dataDxfId="45"/>
+    <tableColumn id="19" xr3:uid="{0A6FA590-01CE-B142-8995-01E614C22035}" name="max" dataDxfId="44">
       <calculatedColumnFormula>MAX($H2:$S2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9232,51 +10622,51 @@
     <sortCondition ref="B22:B28"/>
   </sortState>
   <tableColumns count="19">
-    <tableColumn id="18" xr3:uid="{577483EB-FB0A-C641-99EA-AC0D2A721A13}" name="attribute.index" dataDxfId="64"/>
+    <tableColumn id="18" xr3:uid="{577483EB-FB0A-C641-99EA-AC0D2A721A13}" name="attribute.index" dataDxfId="43"/>
     <tableColumn id="1" xr3:uid="{9E384792-E0EB-8E46-A832-7879C7B9D752}" name="attribute"/>
     <tableColumn id="2" xr3:uid="{09A686DB-85A0-F84C-A351-8E9644F5E7F4}" name="supplemented"/>
     <tableColumn id="3" xr3:uid="{50001403-32D4-1E40-A2DE-F53CC746572A}" name="method.index"/>
     <tableColumn id="4" xr3:uid="{14A6A7EF-F68E-4E45-A8D7-9A3D0AED99E0}" name="method"/>
-    <tableColumn id="19" xr3:uid="{05B77C94-1C48-0F46-9A4A-150843300441}" name="var" dataDxfId="63">
+    <tableColumn id="19" xr3:uid="{05B77C94-1C48-0F46-9A4A-150843300441}" name="var" dataDxfId="42">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.attr,Table61888[[#This Row],[attribute]],_xlpm.spl,LEFT(Table61888[[#This Row],[supplemented]],1),_xlfn.TEXTJOIN("-",TRUE,_xlpm.attr,_xlpm.spl,"3k-mgv3"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EB596FA2-FB7B-CD48-AC8A-469513D551CC}" name="2g-no-hash" dataDxfId="62">
+    <tableColumn id="5" xr3:uid="{EB596FA2-FB7B-CD48-AC8A-469513D551CC}" name="2g-no-hash" dataDxfId="41">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{514D82AC-15FF-164C-A57E-982E62F76D7C}" name="3g-no-hash" dataDxfId="61">
+    <tableColumn id="6" xr3:uid="{514D82AC-15FF-164C-A57E-982E62F76D7C}" name="3g-no-hash" dataDxfId="40">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9BD6AB18-9FDD-4348-982D-5D11516CE46D}" name="4g-no-hash" dataDxfId="60">
+    <tableColumn id="7" xr3:uid="{9BD6AB18-9FDD-4348-982D-5D11516CE46D}" name="4g-no-hash" dataDxfId="39">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9CC50E1B-ACAC-2F45-869B-8472F39EC39D}" name="xsk2g-no-hash" dataDxfId="59">
+    <tableColumn id="8" xr3:uid="{9CC50E1B-ACAC-2F45-869B-8472F39EC39D}" name="xsk2g-no-hash" dataDxfId="38">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{26FBC7FD-8BD9-A543-AD2C-5396921ACC00}" name="xsk3g-no-hash" dataDxfId="58">
+    <tableColumn id="9" xr3:uid="{26FBC7FD-8BD9-A543-AD2C-5396921ACC00}" name="xsk3g-no-hash" dataDxfId="37">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{3BC7A1E2-2436-8349-A84B-F102A21E86F8}" name="xsk4g-no-hash" dataDxfId="57">
+    <tableColumn id="10" xr3:uid="{3BC7A1E2-2436-8349-A84B-F102A21E86F8}" name="xsk4g-no-hash" dataDxfId="36">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2627849E-6227-3B4A-94AA-5DB998E2E22A}" name="2g-hash-at-both" dataDxfId="56">
+    <tableColumn id="11" xr3:uid="{2627849E-6227-3B4A-94AA-5DB998E2E22A}" name="2g-hash-at-both" dataDxfId="35">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{C54AB2DE-57D3-B240-AE10-407A05989552}" name="3g-hash-at-both" dataDxfId="55">
+    <tableColumn id="12" xr3:uid="{C54AB2DE-57D3-B240-AE10-407A05989552}" name="3g-hash-at-both" dataDxfId="34">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{F2152E0C-6EC2-814D-9B8C-E2D1C7BCD91A}" name="4g-hash-at-both" dataDxfId="54">
+    <tableColumn id="13" xr3:uid="{F2152E0C-6EC2-814D-9B8C-E2D1C7BCD91A}" name="4g-hash-at-both" dataDxfId="33">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{350A18F8-E706-5643-918F-9A3017F47C04}" name="xsk2g-hash-at-both" dataDxfId="53">
+    <tableColumn id="14" xr3:uid="{350A18F8-E706-5643-918F-9A3017F47C04}" name="xsk2g-hash-at-both" dataDxfId="32">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{3BD5617A-3301-434C-A6C3-4AC348F666FA}" name="xsk3g-hash-at-both" dataDxfId="52">
+    <tableColumn id="15" xr3:uid="{3BD5617A-3301-434C-A6C3-4AC348F666FA}" name="xsk3g-hash-at-both" dataDxfId="31">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F480B322-4FE6-3B4E-9779-ED4AE6FEA768}" name="xsk4g-hash-at-both" dataDxfId="51">
+    <tableColumn id="16" xr3:uid="{F480B322-4FE6-3B4E-9779-ED4AE6FEA768}" name="xsk4g-hash-at-both" dataDxfId="30">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{508012B1-9F3A-4242-8618-E986642407D1}" name="max" dataDxfId="50">
+    <tableColumn id="17" xr3:uid="{508012B1-9F3A-4242-8618-E986642407D1}" name="max" dataDxfId="29">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9297,22 +10687,22 @@
     <tableColumn id="4" xr3:uid="{BB46AE22-E25A-BB47-8F18-8F47462C8C82}" name="supplemented"/>
     <tableColumn id="5" xr3:uid="{F4575404-5551-A94E-9C26-CE41B91E2CB1}" name="method.index"/>
     <tableColumn id="6" xr3:uid="{BE66ACE7-C3E2-9A4C-AF42-CA79478E6B5A}" name="method"/>
-    <tableColumn id="20" xr3:uid="{9059D89F-2A88-EF4A-B6BB-74835CB70EA3}" name="var" dataDxfId="16">
+    <tableColumn id="20" xr3:uid="{9059D89F-2A88-EF4A-B6BB-74835CB70EA3}" name="var" dataDxfId="28">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.attr,Table1[[#This Row],[attribute]],_xlpm.spl,LEFT(Table1[[#This Row],[supplemented]],1),_xlfn.TEXTJOIN("-",TRUE,_xlpm.attr,_xlpm.spl,"3k-mgv3"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{4EC3AC26-BD44-DC46-97E9-D15442FB1B96}" name="2g-no-hash" dataDxfId="131"/>
-    <tableColumn id="8" xr3:uid="{BEDC43AD-74A5-FC4C-83F5-02DE0FD6AA21}" name="3g-no-hash" dataDxfId="130"/>
-    <tableColumn id="9" xr3:uid="{737E06B2-6A4A-9C47-8A9E-0AE99214A7B9}" name="4g-no-hash" dataDxfId="129"/>
-    <tableColumn id="10" xr3:uid="{1ABFDE72-C84B-E849-85A3-2364EFA02406}" name="xsk2g-no-hash" dataDxfId="128"/>
-    <tableColumn id="11" xr3:uid="{0E077D85-24E7-A649-A557-34726D8A6D92}" name="xsk3g-no-hash" dataDxfId="127"/>
-    <tableColumn id="12" xr3:uid="{D5F82FCC-FE6E-BA43-9FA3-6BD498959E1D}" name="xsk4g-no-hash" dataDxfId="126"/>
-    <tableColumn id="13" xr3:uid="{EEA7C018-AA5A-C941-AED4-48CC01247DF7}" name="2g-hash-at-both" dataDxfId="125"/>
-    <tableColumn id="14" xr3:uid="{F6254348-0E50-244B-A2F2-E2993861B347}" name="3g-hash-at-both" dataDxfId="124"/>
-    <tableColumn id="15" xr3:uid="{57D41874-2DB5-ED46-9135-2BDDAB9DA8F2}" name="4g-hash-at-both" dataDxfId="123"/>
-    <tableColumn id="16" xr3:uid="{8F47C9D1-6E87-DB4B-8826-3174C889BD24}" name="xsk2g-hash-at-both" dataDxfId="122"/>
-    <tableColumn id="17" xr3:uid="{DE7A8535-68D5-C342-9460-9D41B2C95AE8}" name="xsk3g-hash-at-both" dataDxfId="121"/>
-    <tableColumn id="18" xr3:uid="{80C9ACD7-A8A8-674E-9B8C-98347DBDA044}" name="xsk4g-hash-at-both" dataDxfId="120"/>
-    <tableColumn id="19" xr3:uid="{384558E1-0AEC-C943-BFEB-7B79565A6F7B}" name="max" dataDxfId="119">
+    <tableColumn id="7" xr3:uid="{4EC3AC26-BD44-DC46-97E9-D15442FB1B96}" name="2g-no-hash" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{BEDC43AD-74A5-FC4C-83F5-02DE0FD6AA21}" name="3g-no-hash" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{737E06B2-6A4A-9C47-8A9E-0AE99214A7B9}" name="4g-no-hash" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{1ABFDE72-C84B-E849-85A3-2364EFA02406}" name="xsk2g-no-hash" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{0E077D85-24E7-A649-A557-34726D8A6D92}" name="xsk3g-no-hash" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{D5F82FCC-FE6E-BA43-9FA3-6BD498959E1D}" name="xsk4g-no-hash" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{EEA7C018-AA5A-C941-AED4-48CC01247DF7}" name="2g-hash-at-both" dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{F6254348-0E50-244B-A2F2-E2993861B347}" name="3g-hash-at-both" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{57D41874-2DB5-ED46-9135-2BDDAB9DA8F2}" name="4g-hash-at-both" dataDxfId="19"/>
+    <tableColumn id="16" xr3:uid="{8F47C9D1-6E87-DB4B-8826-3174C889BD24}" name="xsk2g-hash-at-both" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{DE7A8535-68D5-C342-9460-9D41B2C95AE8}" name="xsk3g-hash-at-both" dataDxfId="17"/>
+    <tableColumn id="18" xr3:uid="{80C9ACD7-A8A8-674E-9B8C-98347DBDA044}" name="xsk4g-hash-at-both" dataDxfId="16"/>
+    <tableColumn id="19" xr3:uid="{384558E1-0AEC-C943-BFEB-7B79565A6F7B}" name="max" dataDxfId="15">
       <calculatedColumnFormula>MAX($H2:$S2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9327,51 +10717,51 @@
     <sortCondition ref="B22:B28"/>
   </sortState>
   <tableColumns count="19">
-    <tableColumn id="18" xr3:uid="{9C584835-57AB-9947-8CBE-3ADF92BD26D1}" name="attribute.index" dataDxfId="79"/>
+    <tableColumn id="18" xr3:uid="{9C584835-57AB-9947-8CBE-3ADF92BD26D1}" name="attribute.index" dataDxfId="14"/>
     <tableColumn id="1" xr3:uid="{1EAA29A7-11BC-2442-A964-B99434569678}" name="attribute"/>
     <tableColumn id="2" xr3:uid="{1A93C1AD-3BE3-704A-A545-39DBBCCD9DEA}" name="supplemented"/>
     <tableColumn id="3" xr3:uid="{92E7F563-BDE8-B84B-B375-B390788B10AA}" name="method.index"/>
     <tableColumn id="4" xr3:uid="{F22145A7-26C3-434D-953F-6F1F6FCAE5A7}" name="method"/>
-    <tableColumn id="19" xr3:uid="{2425D883-A1BD-0C43-969B-9F5ADECE1AE8}" name="var" dataDxfId="78">
+    <tableColumn id="19" xr3:uid="{2425D883-A1BD-0C43-969B-9F5ADECE1AE8}" name="var" dataDxfId="13">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.attr,Table6188[[#This Row],[attribute]],_xlpm.spl,LEFT(Table6188[[#This Row],[supplemented]],1),_xlfn.TEXTJOIN("-",TRUE,_xlpm.attr,_xlpm.spl,"3k-mgv3"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BA268A6D-120B-7246-8496-4B13062EC26F}" name="2g-no-hash" dataDxfId="77">
+    <tableColumn id="5" xr3:uid="{BA268A6D-120B-7246-8496-4B13062EC26F}" name="2g-no-hash" dataDxfId="12">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{3D5F1BC9-50AA-8A4D-94CE-B1903D2EA559}" name="3g-no-hash" dataDxfId="76">
+    <tableColumn id="6" xr3:uid="{3D5F1BC9-50AA-8A4D-94CE-B1903D2EA559}" name="3g-no-hash" dataDxfId="11">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{E2B17C53-5C3B-0140-953E-D2316DAE140E}" name="4g-no-hash" dataDxfId="75">
+    <tableColumn id="7" xr3:uid="{E2B17C53-5C3B-0140-953E-D2316DAE140E}" name="4g-no-hash" dataDxfId="10">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{89DE8AC7-AAF9-B440-92B2-4129686EDFE9}" name="xsk2g-no-hash" dataDxfId="74">
+    <tableColumn id="8" xr3:uid="{89DE8AC7-AAF9-B440-92B2-4129686EDFE9}" name="xsk2g-no-hash" dataDxfId="9">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{27DF6BE1-3F64-E44F-AB9C-1E4048B1F7D4}" name="xsk3g-no-hash" dataDxfId="73">
+    <tableColumn id="9" xr3:uid="{27DF6BE1-3F64-E44F-AB9C-1E4048B1F7D4}" name="xsk3g-no-hash" dataDxfId="8">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{5497137B-5438-5F41-A721-F2AAFAC22902}" name="xsk4g-no-hash" dataDxfId="72">
+    <tableColumn id="10" xr3:uid="{5497137B-5438-5F41-A721-F2AAFAC22902}" name="xsk4g-no-hash" dataDxfId="7">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{5D54CF33-D8F8-6340-9189-5CC38EDDF051}" name="2g-hash-at-both" dataDxfId="71">
+    <tableColumn id="11" xr3:uid="{5D54CF33-D8F8-6340-9189-5CC38EDDF051}" name="2g-hash-at-both" dataDxfId="6">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9A3EF50E-19C0-8C43-B21C-1AA818519642}" name="3g-hash-at-both" dataDxfId="70">
+    <tableColumn id="12" xr3:uid="{9A3EF50E-19C0-8C43-B21C-1AA818519642}" name="3g-hash-at-both" dataDxfId="5">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{9661DA81-45F2-BF42-BD66-7A6405583F71}" name="4g-hash-at-both" dataDxfId="69">
+    <tableColumn id="13" xr3:uid="{9661DA81-45F2-BF42-BD66-7A6405583F71}" name="4g-hash-at-both" dataDxfId="4">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{26EFA519-E47B-FC4C-889E-40E5884C8111}" name="xsk2g-hash-at-both" dataDxfId="68">
+    <tableColumn id="14" xr3:uid="{26EFA519-E47B-FC4C-889E-40E5884C8111}" name="xsk2g-hash-at-both" dataDxfId="3">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2888F11F-C974-4F4C-BFCC-87026D6CF8BD}" name="xsk3g-hash-at-both" dataDxfId="67">
+    <tableColumn id="15" xr3:uid="{2888F11F-C974-4F4C-BFCC-87026D6CF8BD}" name="xsk3g-hash-at-both" dataDxfId="2">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{E4C9CF06-7047-8A46-9C1D-A85AE1EB7545}" name="xsk4g-hash-at-both" dataDxfId="66">
+    <tableColumn id="16" xr3:uid="{E4C9CF06-7047-8A46-9C1D-A85AE1EB7545}" name="xsk4g-hash-at-both" dataDxfId="1">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{0AB8A7EE-8D89-D14D-A774-B8D13F8A6D8C}" name="max" dataDxfId="65">
+    <tableColumn id="17" xr3:uid="{0AB8A7EE-8D89-D14D-A774-B8D13F8A6D8C}" name="max" dataDxfId="0">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9857,15 +11247,15 @@
         <v>0.76</v>
       </c>
       <c r="X2" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K2:$V2,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" ref="X2:X33" si="0">_xlfn.LET(_xlpm.d,$K2:$V2,GEOMEAN(_xlpm.d))</f>
         <v>0.71947406565044059</v>
       </c>
       <c r="Y2" s="4">
-        <f>RANK(X2,X$2:X$67)</f>
+        <f t="shared" ref="Y2:Y33" si="1">RANK(X2,X$2:X$67)</f>
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="3" spans="1:25" ht="25" customHeight="1">
       <c r="A3">
         <v>3</v>
       </c>
@@ -9937,15 +11327,15 @@
         <v>0.86</v>
       </c>
       <c r="X3" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K3:$V3,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.70719046918728912</v>
       </c>
       <c r="Y3" s="4">
-        <f>RANK(X3,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="4" spans="1:25" ht="25" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -10017,15 +11407,15 @@
         <v>0.76</v>
       </c>
       <c r="X4" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K4:$V4,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.70268659346669438</v>
       </c>
       <c r="Y4" s="4">
-        <f>RANK(X4,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="5" spans="1:25" ht="25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -10097,11 +11487,11 @@
         <v>0.77</v>
       </c>
       <c r="X5" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K5:$V5,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.70161076993954963</v>
       </c>
       <c r="Y5" s="4">
-        <f>RANK(X5,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
     </row>
@@ -10177,15 +11567,15 @@
         <v>0.76</v>
       </c>
       <c r="X6" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K6:$V6,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.70091398255778581</v>
       </c>
       <c r="Y6" s="4">
-        <f>RANK(X6,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="7" spans="1:25" ht="25" customHeight="1">
       <c r="A7">
         <v>0</v>
       </c>
@@ -10257,15 +11647,15 @@
         <v>0.74</v>
       </c>
       <c r="X7" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K7:$V7,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.70043693637797755</v>
       </c>
       <c r="Y7" s="4">
-        <f>RANK(X7,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="8" spans="1:25" ht="25" customHeight="1">
       <c r="A8">
         <v>0</v>
       </c>
@@ -10337,15 +11727,15 @@
         <v>0.8</v>
       </c>
       <c r="X8" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K8:$V8,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.69780559955381394</v>
       </c>
       <c r="Y8" s="4">
-        <f>RANK(X8,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="9" spans="1:25" ht="25" customHeight="1">
       <c r="A9">
         <v>2</v>
       </c>
@@ -10417,11 +11807,11 @@
         <v>0.74</v>
       </c>
       <c r="X9" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K9:$V9,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.6970353946167267</v>
       </c>
       <c r="Y9" s="4">
-        <f>RANK(X9,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
     </row>
@@ -10497,15 +11887,15 @@
         <v>0.77</v>
       </c>
       <c r="X10" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K10:$V10,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.69571136965847347</v>
       </c>
       <c r="Y10" s="4">
-        <f>RANK(X10,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="11" spans="1:25" ht="25" customHeight="1">
       <c r="A11">
         <v>3</v>
       </c>
@@ -10577,11 +11967,11 @@
         <v>0.81</v>
       </c>
       <c r="X11" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K11:$V11,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.69357702504594343</v>
       </c>
       <c r="Y11" s="4">
-        <f>RANK(X11,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
     </row>
@@ -10657,15 +12047,15 @@
         <v>0.72</v>
       </c>
       <c r="X12" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K12:$V12,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.68806935657372403</v>
       </c>
       <c r="Y12" s="4">
-        <f>RANK(X12,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="13" spans="1:25" ht="25" customHeight="1">
       <c r="A13">
         <v>0</v>
       </c>
@@ -10737,11 +12127,11 @@
         <v>0.75</v>
       </c>
       <c r="X13" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K13:$V13,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.68665607163074571</v>
       </c>
       <c r="Y13" s="4">
-        <f>RANK(X13,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
     </row>
@@ -10817,11 +12207,11 @@
         <v>0.74</v>
       </c>
       <c r="X14" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K14:$V14,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.68413025262746485</v>
       </c>
       <c r="Y14" s="4">
-        <f>RANK(X14,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
     </row>
@@ -10897,15 +12287,15 @@
         <v>0.76</v>
       </c>
       <c r="X15" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K15:$V15,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.68141283089184357</v>
       </c>
       <c r="Y15" s="4">
-        <f>RANK(X15,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="16" spans="1:25" ht="25" customHeight="1">
       <c r="A16">
         <v>3</v>
       </c>
@@ -10977,11 +12367,11 @@
         <v>0.73</v>
       </c>
       <c r="X16" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K16:$V16,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.68056394298884026</v>
       </c>
       <c r="Y16" s="4">
-        <f>RANK(X16,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
     </row>
@@ -11057,15 +12447,15 @@
         <v>0.77</v>
       </c>
       <c r="X17" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K17:$V17,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.67909631871350229</v>
       </c>
       <c r="Y17" s="4">
-        <f>RANK(X17,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="18" spans="1:25" ht="25" customHeight="1">
       <c r="A18">
         <v>0</v>
       </c>
@@ -11137,15 +12527,15 @@
         <v>0.79</v>
       </c>
       <c r="X18" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K18:$V18,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.67782648889683728</v>
       </c>
       <c r="Y18" s="4">
-        <f>RANK(X18,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="19" spans="1:25" ht="25" customHeight="1">
       <c r="A19">
         <v>0</v>
       </c>
@@ -11217,15 +12607,15 @@
         <v>0.74</v>
       </c>
       <c r="X19" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K19:$V19,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.67479892269766317</v>
       </c>
       <c r="Y19" s="4">
-        <f>RANK(X19,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="20" spans="1:25" ht="25" customHeight="1">
       <c r="A20">
         <v>2</v>
       </c>
@@ -11297,15 +12687,15 @@
         <v>0.74</v>
       </c>
       <c r="X20" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K20:$V20,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.67168278954498906</v>
       </c>
       <c r="Y20" s="4">
-        <f>RANK(X20,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="21" spans="1:25" ht="25" customHeight="1">
       <c r="A21">
         <v>2</v>
       </c>
@@ -11377,15 +12767,15 @@
         <v>0.73</v>
       </c>
       <c r="X21" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K21:$V21,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.67105396583401122</v>
       </c>
       <c r="Y21" s="4">
-        <f>RANK(X21,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="22" spans="1:25" ht="25" customHeight="1">
       <c r="A22">
         <v>0</v>
       </c>
@@ -11457,11 +12847,11 @@
         <v>0.72</v>
       </c>
       <c r="X22" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K22:$V22,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.66191856303065721</v>
       </c>
       <c r="Y22" s="4">
-        <f>RANK(X22,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
     </row>
@@ -11537,11 +12927,11 @@
         <v>0.73</v>
       </c>
       <c r="X23" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K23:$V23,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.65357276686031862</v>
       </c>
       <c r="Y23" s="4">
-        <f>RANK(X23,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
     </row>
@@ -11617,11 +13007,11 @@
         <v>0.83</v>
       </c>
       <c r="X24" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K24:$V24,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.77781458743787679</v>
       </c>
       <c r="Y24" s="4">
-        <f>RANK(X24,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
     </row>
@@ -11697,11 +13087,11 @@
         <v>0.82</v>
       </c>
       <c r="X25" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K25:$V25,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.74288871709948157</v>
       </c>
       <c r="Y25" s="4">
-        <f>RANK(X25,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
     </row>
@@ -11777,11 +13167,11 @@
         <v>0.83</v>
       </c>
       <c r="X26" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K26:$V26,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.76768534142629308</v>
       </c>
       <c r="Y26" s="4">
-        <f>RANK(X26,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
@@ -11857,11 +13247,11 @@
         <v>0.81</v>
       </c>
       <c r="X27" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K27:$V27,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.78643829709659874</v>
       </c>
       <c r="Y27" s="4">
-        <f>RANK(X27,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
     </row>
@@ -11937,11 +13327,11 @@
         <v>0.85</v>
       </c>
       <c r="X28" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K28:$V28,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.77729192553052984</v>
       </c>
       <c r="Y28" s="4">
-        <f>RANK(X28,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
     </row>
@@ -12017,11 +13407,11 @@
         <v>0.84</v>
       </c>
       <c r="X29" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K29:$V29,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.78855979713256041</v>
       </c>
       <c r="Y29" s="4">
-        <f>RANK(X29,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
     </row>
@@ -12097,11 +13487,11 @@
         <v>0.82</v>
       </c>
       <c r="X30" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K30:$V30,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.7685411414917046</v>
       </c>
       <c r="Y30" s="4">
-        <f>RANK(X30,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
     </row>
@@ -12177,11 +13567,11 @@
         <v>0.82</v>
       </c>
       <c r="X31" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K31:$V31,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.76929539910310241</v>
       </c>
       <c r="Y31" s="4">
-        <f>RANK(X31,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
     </row>
@@ -12257,11 +13647,11 @@
         <v>0.82</v>
       </c>
       <c r="X32" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K32:$V32,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.76520402249372532</v>
       </c>
       <c r="Y32" s="4">
-        <f>RANK(X32,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
     </row>
@@ -12337,15 +13727,15 @@
         <v>0.82</v>
       </c>
       <c r="X33" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K33:$V33,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="0"/>
         <v>0.76298416525377621</v>
       </c>
       <c r="Y33" s="4">
-        <f>RANK(X33,X$2:X$67)</f>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="34" spans="1:25" ht="25" customHeight="1">
       <c r="A34">
         <v>2</v>
       </c>
@@ -12417,15 +13807,15 @@
         <v>0.81</v>
       </c>
       <c r="X34" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K34:$V34,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" ref="X34:X67" si="2">_xlfn.LET(_xlpm.d,$K34:$V34,GEOMEAN(_xlpm.d))</f>
         <v>0.75836499757300269</v>
       </c>
       <c r="Y34" s="4">
-        <f>RANK(X34,X$2:X$67)</f>
+        <f t="shared" ref="Y34:Y65" si="3">RANK(X34,X$2:X$67)</f>
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="35" spans="1:25" ht="25" customHeight="1">
       <c r="A35">
         <v>0</v>
       </c>
@@ -12497,15 +13887,15 @@
         <v>0.78</v>
       </c>
       <c r="X35" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K35:$V35,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.75712136506055683</v>
       </c>
       <c r="Y35" s="4">
-        <f>RANK(X35,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="36" spans="1:25" ht="25" customHeight="1">
       <c r="A36">
         <v>3</v>
       </c>
@@ -12577,11 +13967,11 @@
         <v>0.84</v>
       </c>
       <c r="X36" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K36:$V36,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.74635255978469617</v>
       </c>
       <c r="Y36" s="4">
-        <f>RANK(X36,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
     </row>
@@ -12657,11 +14047,11 @@
         <v>0.79</v>
       </c>
       <c r="X37" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K37:$V37,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.74449478095618793</v>
       </c>
       <c r="Y37" s="4">
-        <f>RANK(X37,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
     </row>
@@ -12737,15 +14127,15 @@
         <v>0.85</v>
       </c>
       <c r="X38" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K38:$V38,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.77842918069247502</v>
       </c>
       <c r="Y38" s="4">
-        <f>RANK(X38,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="39" spans="1:25" ht="25" customHeight="1">
       <c r="A39">
         <v>2</v>
       </c>
@@ -12817,11 +14207,11 @@
         <v>0.77</v>
       </c>
       <c r="X39" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K39:$V39,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.74134675660869209</v>
       </c>
       <c r="Y39" s="4">
-        <f>RANK(X39,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>38</v>
       </c>
     </row>
@@ -12897,11 +14287,11 @@
         <v>0.78</v>
       </c>
       <c r="X40" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K40:$V40,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.74113127691303538</v>
       </c>
       <c r="Y40" s="4">
-        <f>RANK(X40,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>39</v>
       </c>
     </row>
@@ -12977,15 +14367,15 @@
         <v>0.83</v>
       </c>
       <c r="X41" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K41:$V41,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.74032663800792753</v>
       </c>
       <c r="Y41" s="4">
-        <f>RANK(X41,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="42" spans="1:25" ht="25" customHeight="1">
       <c r="A42">
         <v>0</v>
       </c>
@@ -13057,11 +14447,11 @@
         <v>0.77</v>
       </c>
       <c r="X42" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K42:$V42,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.73697996718224545</v>
       </c>
       <c r="Y42" s="4">
-        <f>RANK(X42,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
@@ -13137,15 +14527,15 @@
         <v>0.81</v>
       </c>
       <c r="X43" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K43:$V43,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.7349169371442692</v>
       </c>
       <c r="Y43" s="4">
-        <f>RANK(X43,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="44" spans="1:25" ht="25" customHeight="1">
       <c r="A44">
         <v>3</v>
       </c>
@@ -13217,15 +14607,15 @@
         <v>0.8</v>
       </c>
       <c r="X44" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K44:$V44,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.72947072310744387</v>
       </c>
       <c r="Y44" s="4">
-        <f>RANK(X44,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="45" spans="1:25" ht="25" customHeight="1">
       <c r="A45">
         <v>0</v>
       </c>
@@ -13297,11 +14687,11 @@
         <v>0.75</v>
       </c>
       <c r="X45" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K45:$V45,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.71449485264788171</v>
       </c>
       <c r="Y45" s="4">
-        <f>RANK(X45,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
     </row>
@@ -13377,11 +14767,11 @@
         <v>1</v>
       </c>
       <c r="X46" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K46:$V46,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.97569189655850175</v>
       </c>
       <c r="Y46" s="4">
-        <f>RANK(X46,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -13457,15 +14847,15 @@
         <v>1</v>
       </c>
       <c r="X47" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K47:$V47,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.97486678009739391</v>
       </c>
       <c r="Y47" s="4">
-        <f>RANK(X47,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="48" spans="1:25" ht="25" customHeight="1">
       <c r="A48">
         <v>2</v>
       </c>
@@ -13537,15 +14927,15 @@
         <v>0.99</v>
       </c>
       <c r="X48" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K48:$V48,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.97411141550182712</v>
       </c>
       <c r="Y48" s="4">
-        <f>RANK(X48,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="49" spans="1:25" ht="25" customHeight="1">
       <c r="A49">
         <v>0</v>
       </c>
@@ -13617,15 +15007,15 @@
         <v>0.98</v>
       </c>
       <c r="X49" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K49:$V49,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.97330470200028285</v>
       </c>
       <c r="Y49" s="4">
-        <f>RANK(X49,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="50" spans="1:25" ht="25" customHeight="1">
       <c r="A50">
         <v>3</v>
       </c>
@@ -13697,15 +15087,15 @@
         <v>1</v>
       </c>
       <c r="X50" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K50:$V50,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.97314012600486277</v>
       </c>
       <c r="Y50" s="4">
-        <f>RANK(X50,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="51" spans="1:25" ht="25" customHeight="1">
       <c r="A51">
         <v>2</v>
       </c>
@@ -13777,15 +15167,15 @@
         <v>0.99</v>
       </c>
       <c r="X51" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K51:$V51,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.97243906243998646</v>
       </c>
       <c r="Y51" s="4">
-        <f>RANK(X51,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="52" spans="1:25" ht="25" customHeight="1">
       <c r="A52">
         <v>3</v>
       </c>
@@ -13857,15 +15247,15 @@
         <v>0.99</v>
       </c>
       <c r="X52" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K52:$V52,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.97236942717285868</v>
       </c>
       <c r="Y52" s="4">
-        <f>RANK(X52,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="53" spans="1:25" ht="25" customHeight="1">
       <c r="A53">
         <v>0</v>
       </c>
@@ -13937,15 +15327,15 @@
         <v>0.98</v>
       </c>
       <c r="X53" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K53:$V53,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.97164233993335203</v>
       </c>
       <c r="Y53" s="4">
-        <f>RANK(X53,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="54" spans="1:25" ht="25" customHeight="1">
       <c r="A54">
         <v>2</v>
       </c>
@@ -14017,15 +15407,15 @@
         <v>0.99</v>
       </c>
       <c r="X54" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K54:$V54,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.96826644194537137</v>
       </c>
       <c r="Y54" s="4">
-        <f>RANK(X54,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="55" spans="1:25" ht="25" customHeight="1">
       <c r="A55">
         <v>2</v>
       </c>
@@ -14097,11 +15487,11 @@
         <v>0.99</v>
       </c>
       <c r="X55" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K55:$V55,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.96826644194537137</v>
       </c>
       <c r="Y55" s="4">
-        <f>RANK(X55,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
     </row>
@@ -14177,11 +15567,11 @@
         <v>0.99</v>
       </c>
       <c r="X56" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K56:$V56,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.966533280400106</v>
       </c>
       <c r="Y56" s="4">
-        <f>RANK(X56,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
@@ -14257,15 +15647,15 @@
         <v>0.99</v>
       </c>
       <c r="X57" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K57:$V57,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.966533280400106</v>
       </c>
       <c r="Y57" s="4">
-        <f>RANK(X57,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="58" spans="1:25" ht="25" customHeight="1">
       <c r="A58">
         <v>0</v>
       </c>
@@ -14337,15 +15727,15 @@
         <v>0.99</v>
       </c>
       <c r="X58" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K58:$V58,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.96490921944976515</v>
       </c>
       <c r="Y58" s="4">
-        <f>RANK(X58,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="59" spans="1:25" ht="25" customHeight="1">
       <c r="A59">
         <v>0</v>
       </c>
@@ -14417,11 +15807,11 @@
         <v>0.98</v>
       </c>
       <c r="X59" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K59:$V59,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.96409322160941102</v>
       </c>
       <c r="Y59" s="4">
-        <f>RANK(X59,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -14497,11 +15887,11 @@
         <v>0.98</v>
       </c>
       <c r="X60" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K60:$V60,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.96329587162534192</v>
       </c>
       <c r="Y60" s="4">
-        <f>RANK(X60,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
@@ -14577,11 +15967,11 @@
         <v>0.98</v>
       </c>
       <c r="X61" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K61:$V61,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.96242084030510444</v>
       </c>
       <c r="Y61" s="4">
-        <f>RANK(X61,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -14657,11 +16047,11 @@
         <v>0.98</v>
       </c>
       <c r="X62" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K62:$V62,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.96160729813767365</v>
       </c>
       <c r="Y62" s="4">
-        <f>RANK(X62,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -14737,15 +16127,15 @@
         <v>0.98</v>
       </c>
       <c r="X63" s="1">
-        <f>_xlfn.LET(_xlpm.d,$K63:$V63,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.96075099793581509</v>
       </c>
       <c r="Y63" s="4">
-        <f>RANK(X63,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="64" spans="1:25" ht="25" customHeight="1">
       <c r="A64">
         <v>0</v>
       </c>
@@ -14817,15 +16207,15 @@
         <v>0.98</v>
       </c>
       <c r="X64" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K64:$V64,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.9607062373580324</v>
       </c>
       <c r="Y64" s="4">
-        <f>RANK(X64,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="65" spans="1:25" ht="25" customHeight="1">
       <c r="A65">
         <v>0</v>
       </c>
@@ -14897,15 +16287,15 @@
         <v>0.98</v>
       </c>
       <c r="X65" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K65:$V65,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.95900314702218747</v>
       </c>
       <c r="Y65" s="4">
-        <f>RANK(X65,X$2:X$67)</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="66" spans="1:25" ht="25" customHeight="1">
       <c r="A66">
         <v>3</v>
       </c>
@@ -14977,15 +16367,15 @@
         <v>0.98</v>
       </c>
       <c r="X66" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K66:$V66,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.95824823542334381</v>
       </c>
       <c r="Y66" s="4">
-        <f>RANK(X66,X$2:X$67)</f>
+        <f t="shared" ref="Y66:Y97" si="4">RANK(X66,X$2:X$67)</f>
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="25" hidden="1" customHeight="1">
+    <row r="67" spans="1:25" ht="25" customHeight="1">
       <c r="A67">
         <v>3</v>
       </c>
@@ -15057,11 +16447,11 @@
         <v>0.98</v>
       </c>
       <c r="X67" s="3">
-        <f>_xlfn.LET(_xlpm.d,$K67:$V67,GEOMEAN(_xlpm.d))</f>
+        <f t="shared" si="2"/>
         <v>0.95740358393675917</v>
       </c>
       <c r="Y67" s="4">
-        <f>RANK(X67,X$2:X$67)</f>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
     </row>
